--- a/data/trans_camb/P32-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,01</t>
+          <t>1,05; 10,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 7,26</t>
+          <t>-1,84; 6,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 12,27</t>
+          <t>-3,86; 12,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,14</t>
+          <t>-3,57; 3,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 9,56</t>
+          <t>-0,05; 9,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 12,08</t>
+          <t>-1,88; 12,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,42</t>
+          <t>0,22; 6,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,48</t>
+          <t>-0,25; 6,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 9,39</t>
+          <t>-1,99; 9,01</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 297,68</t>
+          <t>15,12; 326,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 210,07</t>
+          <t>-28,04; 189,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 349,03</t>
+          <t>-65,17; 325,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-85,05; 277,2</t>
+          <t>-77,13; 412,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 675,03</t>
+          <t>-14,79; 1043,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,14; 1008,89</t>
+          <t>-76,86; 1281,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 219,2</t>
+          <t>0,75; 196,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 217,16</t>
+          <t>-7,69; 210,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 306,14</t>
+          <t>-43,41; 304,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,38</t>
+          <t>2,08; 8,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,3</t>
+          <t>0,76; 7,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 9,47</t>
+          <t>0,43; 9,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,15</t>
+          <t>-0,3; 6,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,54</t>
+          <t>-0,18; 5,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 7,08</t>
+          <t>-0,77; 7,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,8</t>
+          <t>2,13; 6,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,71</t>
+          <t>1,22; 5,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,0</t>
+          <t>0,48; 7,06</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,91; 443,07</t>
+          <t>39,76; 405,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 346,97</t>
+          <t>13,6; 361,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 409,22</t>
+          <t>-0,26; 408,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,13; —</t>
+          <t>-65,51; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,07; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,98; 429,82</t>
+          <t>56,63; 402,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,87; 378,09</t>
+          <t>33,59; 334,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 387,14</t>
+          <t>8,38; 391,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,31</t>
+          <t>1,32; 6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,45</t>
+          <t>0,24; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,12</t>
+          <t>2,37; 8,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,35</t>
+          <t>-0,17; 5,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,82</t>
+          <t>-1,85; 1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,67</t>
+          <t>-0,88; 3,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,95</t>
+          <t>1,6; 5,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,79</t>
+          <t>-0,01; 2,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,4</t>
+          <t>1,78; 6,43</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,66; 1222,56</t>
+          <t>24,51; 1190,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 799,3</t>
+          <t>-8,62; 1107,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,87; 1611,06</t>
+          <t>90,88; 2002,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,62; —</t>
+          <t>-65,46; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-97,57; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,03; 784,73</t>
+          <t>65,85; 927,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 510,29</t>
+          <t>-9,35; 478,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75,72; 1078,62</t>
+          <t>76,52; 1016,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,61</t>
+          <t>3,01; 9,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,64</t>
+          <t>2,83; 8,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,01</t>
+          <t>0,72; 6,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,0</t>
+          <t>-5,1; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,93</t>
+          <t>-1,3; 4,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,71</t>
+          <t>-2,6; 2,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,12</t>
+          <t>1,37; 6,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,13</t>
+          <t>1,88; 6,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,01</t>
+          <t>0,2; 4,08</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,75; 2349,7</t>
+          <t>79,85; 2392,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56,87; 2134,62</t>
+          <t>72,53; 1997,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 1491,96</t>
+          <t>-2,96; 1470,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,88; —</t>
+          <t>-63,84; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,56; —</t>
+          <t>-86,08; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,05; 1064,98</t>
+          <t>37,97; 1078,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>57,41; 1119,27</t>
+          <t>60,67; 1141,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 710,44</t>
+          <t>-13,7; 771,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,39</t>
+          <t>-6,24; 2,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 4,7</t>
+          <t>-4,63; 4,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 8,21</t>
+          <t>-0,9; 8,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,81</t>
+          <t>-4,88; 1,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,19</t>
+          <t>-3,1; 6,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,06</t>
+          <t>-2,54; 4,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,25</t>
+          <t>-4,67; 1,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,12</t>
+          <t>-2,69; 4,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 6,42</t>
+          <t>-0,6; 6,32</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-79,74; 93,96</t>
+          <t>-78,87; 93,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 158,68</t>
+          <t>-58,6; 161,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 238,18</t>
+          <t>-19,6; 266,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 62,39</t>
+          <t>-79,75; 83,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 153,39</t>
+          <t>-49,45; 159,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 267,97</t>
+          <t>-13,19; 255,56</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 10,59</t>
+          <t>0,05; 10,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,72</t>
+          <t>-5,86; 1,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,96</t>
+          <t>-0,29; 7,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 7,39</t>
+          <t>-1,06; 7,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,69</t>
+          <t>-4,17; 1,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 4,06</t>
+          <t>-4,49; 3,9</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-61,22; —</t>
+          <t>-50,93; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-49,85; —</t>
+          <t>-31,98; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,83; —</t>
+          <t>-57,05; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,68; 801,61</t>
+          <t>-81,54; 1135,86</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 9,2</t>
+          <t>-2,72; 10,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,75</t>
+          <t>-2,81; 6,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,0</t>
+          <t>-5,43; 1,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,88</t>
+          <t>-2,27; 8,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,8</t>
+          <t>-2,28; 4,67</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,1</t>
+          <t>-3,39; 2,3</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,46</t>
+          <t>2,65; 5,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,94</t>
+          <t>1,17; 3,75</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,06</t>
+          <t>1,94; 5,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,99</t>
+          <t>-0,66; 1,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,09</t>
+          <t>0,42; 3,12</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,34</t>
+          <t>-0,83; 2,34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,99</t>
+          <t>1,78; 3,88</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,31</t>
+          <t>1,26; 3,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,5</t>
+          <t>1,02; 3,55</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>77,48; 238,34</t>
+          <t>77,3; 239,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>38,6; 171,03</t>
+          <t>32,65; 166,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>57,58; 217,73</t>
+          <t>60,16; 230,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 213,3</t>
+          <t>-36,52; 204,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>17,55; 339,74</t>
+          <t>16,78; 379,73</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 222,15</t>
+          <t>-34,57; 268,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,46; 205,15</t>
+          <t>61,39; 195,12</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>41,18; 165,44</t>
+          <t>43,92; 168,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>38,68; 173,03</t>
+          <t>34,37; 173,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,03</t>
+          <t>0,8; 10,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,83</t>
+          <t>-1,89; 7,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 12,4</t>
+          <t>-2,82; 12,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,42</t>
+          <t>-3,57; 3,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 9,2</t>
+          <t>-0,3; 8,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 12,31</t>
+          <t>-0,64; 14,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,26</t>
+          <t>0,23; 6,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,57</t>
+          <t>0,31; 6,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 9,01</t>
+          <t>-0,25; 10,56</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>105,89%</t>
+          <t>197,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 326,82</t>
+          <t>4,31; 297,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 189,61</t>
+          <t>-34,69; 216,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 325,48</t>
+          <t>-51,8; 366,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 412,87</t>
+          <t>-80,88; 320,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 1043,29</t>
+          <t>-21,31; 760,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 1281,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 196,1</t>
+          <t>1,63; 211,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 210,96</t>
+          <t>-0,47; 205,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 304,93</t>
+          <t>-12,07; 324,14</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>3,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,09</t>
+          <t>1,75; 8,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,23</t>
+          <t>1,27; 7,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,6</t>
+          <t>0,93; 9,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,55</t>
+          <t>-0,04; 6,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,52</t>
+          <t>-0,35; 5,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 7,72</t>
+          <t>-0,77; 7,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,67</t>
+          <t>2,17; 6,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,7</t>
+          <t>1,03; 5,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,06</t>
+          <t>0,71; 6,67</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130,58%</t>
+          <t>144,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>197,89%</t>
+          <t>190,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>130,02%</t>
+          <t>139,41%</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,76; 405,28</t>
+          <t>37,02; 394,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 361,57</t>
+          <t>22,21; 338,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 408,0</t>
+          <t>16,17; 447,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,51; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,0; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,63; 402,29</t>
+          <t>50,91; 389,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,59; 334,41</t>
+          <t>27,97; 330,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 391,37</t>
+          <t>16,74; 372,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>4,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,13</t>
+          <t>1,4; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,33</t>
+          <t>0,17; 4,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,87</t>
+          <t>3,2; 9,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,65</t>
+          <t>-0,24; 5,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,79</t>
+          <t>-1,68; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,87</t>
+          <t>-1,33; 3,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,24</t>
+          <t>1,39; 5,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,64</t>
+          <t>-0,08; 2,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,43</t>
+          <t>2,13; 6,59</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>417,42%</t>
+          <t>482,36%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>131,35%</t>
+          <t>120,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>332,89%</t>
+          <t>373,56%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,51; 1190,08</t>
+          <t>48,82; 1073,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1107,0</t>
+          <t>-11,82; 789,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,88; 2002,34</t>
+          <t>116,68; 1856,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,46; —</t>
+          <t>-74,82; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-97,57; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,85; 927,53</t>
+          <t>63,28; 818,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 478,76</t>
+          <t>-15,87; 465,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,52; 1016,54</t>
+          <t>113,35; 1252,4</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,65</t>
+          <t>3,13; 9,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,31</t>
+          <t>2,53; 8,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,18</t>
+          <t>1,07; 6,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,0</t>
+          <t>-5,37; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,89</t>
+          <t>-1,58; 4,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,61</t>
+          <t>-2,39; 3,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,04</t>
+          <t>1,37; 5,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,29</t>
+          <t>1,85; 6,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,08</t>
+          <t>0,55; 4,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>272,94%</t>
+          <t>283,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>175,55%</t>
+          <t>189,67%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,85; 2392,51</t>
+          <t>72,92; 2353,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72,53; 1997,64</t>
+          <t>48,66; 2052,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1470,71</t>
+          <t>-1,94; 1645,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,84; —</t>
+          <t>-77,08; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,08; —</t>
+          <t>-78,78; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,97; 1078,8</t>
+          <t>41,91; 1048,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,67; 1141,72</t>
+          <t>60,93; 1209,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 771,13</t>
+          <t>10,06; 730,26</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,29</t>
+          <t>-6,28; 2,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 4,62</t>
+          <t>-4,39; 4,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 8,3</t>
+          <t>-1,65; 7,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,83</t>
+          <t>-5,55; 1,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,38</t>
+          <t>-1,96; 6,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,94</t>
+          <t>-2,14; 4,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,68</t>
+          <t>-4,84; 1,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,08</t>
+          <t>-2,78; 3,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,32</t>
+          <t>-0,86; 5,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>156,65%</t>
+          <t>151,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 93,46</t>
+          <t>-78,8; 108,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,6; 161,92</t>
+          <t>-58,91; 157,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 266,23</t>
+          <t>-21,92; 262,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 83,65</t>
+          <t>-78,05; 64,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 159,15</t>
+          <t>-50,54; 146,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 255,56</t>
+          <t>-24,69; 229,05</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>3,63</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,05; 10,67</t>
+          <t>-0,61; 11,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,59</t>
+          <t>-5,78; 1,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 7,8</t>
+          <t>-0,41; 7,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,58; 6,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,36</t>
+          <t>-0,8; 7,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,68</t>
+          <t>-4,2; 1,74</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,9</t>
+          <t>-0,14; 6,47</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>217,95%</t>
+          <t>229,83%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>229,98%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,93; —</t>
+          <t>-68,29; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,98; —</t>
+          <t>-37,45; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,05; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 1135,86</t>
+          <t>-31,68; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 10,41</t>
+          <t>-2,76; 10,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 6,18</t>
+          <t>-2,71; 6,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,96</t>
+          <t>-4,83; 2,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,24</t>
+          <t>-2,22; 8,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,67</t>
+          <t>-2,3; 4,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,3</t>
+          <t>-3,21; 2,92</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-9,08%</t>
+          <t>-10,4%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,41</t>
+          <t>2,68; 5,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,75</t>
+          <t>1,32; 3,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,11</t>
+          <t>2,27; 5,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,92</t>
+          <t>-0,57; 2,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,12</t>
+          <t>0,45; 3,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,34</t>
+          <t>0,56; 3,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,88</t>
+          <t>1,86; 3,93</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,22</t>
+          <t>1,3; 3,24</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,55</t>
+          <t>2,09; 4,3</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>126,06%</t>
+          <t>137,34%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>133,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>101,1%</t>
+          <t>132,81%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>77,3; 239,37</t>
+          <t>84,0; 248,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>32,65; 166,84</t>
+          <t>39,89; 173,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>60,16; 230,78</t>
+          <t>66,94; 250,37</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 204,3</t>
+          <t>-29,65; 231,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,78; 379,73</t>
+          <t>16,4; 353,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 268,77</t>
+          <t>22,06; 376,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,39; 195,12</t>
+          <t>65,59; 203,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>43,92; 168,79</t>
+          <t>45,83; 165,47</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34,37; 173,14</t>
+          <t>75,12; 224,5</t>
         </is>
       </c>
     </row>
